--- a/Result/profitability/1109.xlsx
+++ b/Result/profitability/1109.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.22625</v>
+        <v>0.22125</v>
       </c>
       <c r="N2" t="n">
-        <v>16.0625</v>
+        <v>15.335</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2</v>
+        <v>0.18125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.585</v>
+        <v>14.15375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18</v>
+        <v>0.16625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.9975</v>
+        <v>14.1425</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15375</v>
+        <v>0.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>14.00125</v>
+        <v>12.85625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.135</v>
+        <v>0.11375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.76125</v>
+        <v>13.09375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.10625</v>
+        <v>0.095</v>
       </c>
       <c r="N7" t="n">
-        <v>14.05125</v>
+        <v>13.6725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.10375</v>
       </c>
       <c r="N8" t="n">
-        <v>14.4325</v>
+        <v>15.1025</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D75" t="n">
+        <v>886</v>
+      </c>
+      <c r="E75" t="n">
+        <v>116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>47</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>62</v>
+      </c>
+      <c r="K75" t="n">
+        <v>46</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.359999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.8603531300160512</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4166666666666666</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4414457831325301</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
